--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3262,6 +3262,3134 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B1VS7ID2GL</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-10-06T18:43:16.449Z</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BKHV0XAFEG</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Orçamento teste</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2025-09-04T16:01:06.048Z</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ODBiZWNhYTUtOGMwYS00OGM1LWI4MGQtYjZhYzUyNzk3ZDg2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S104AAJU-L</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rele de estado sólido - 21256870000287 - FERRO + MINERACAO S.A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Rele do estado sólido</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>660.525</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>660.525</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-01-29T17:13:31.699Z</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Lucas Uenishi Tada</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-01-22T17:24:06.452Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NDgyNDM2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>MTU0OGJhYjItYzE4NS00NGNmLThhOGItYzA1MzhmNTNjODJlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OGFmODc0N2UtMGFlMy00NjU1LWE5NTctY2RiZGU4NDljYjAxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>R1PHKJKUBL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Visita Técnica para problemas no alarme - 90400888000142 - BANCO SANTANDER (BRASIL) S/A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Possível falha no sensor ou alarme de sobrecarga</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-01-29T12:16:04.953Z</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Lucas Uenishi Tada</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-01-22T13:01:41.368Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>MzMzMDQ1Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>YmEwMmQ1NzItYmIwMi00NTAxLWI4NWYtYmZiODY3NjIwZmRhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>R1R8PTIYBL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>orçamento</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2025-11-10T19:48:40.136Z</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>MmJlOTE4ZTYtMjdkMy00NThjLWE0ODUtYjczNjgwYjM3NWJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HK9JZSR83</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TESTE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TESTE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2023-06-07T21:55:05.692Z</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>YmViOGRmMjAtM2EwYy00NTFkLTkwNzctODkwYmM4MzA5NGQ0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BJ0FAVCKBL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MAQUINA 01</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Autorizado por João</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1298.9</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1298.9</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2025-11-13T15:27:58.539Z</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S1SWKWAKXG</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2025-08-28T16:10:11.398Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BKMVCD56XX</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>40.894999999999996</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>40.894999999999996</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2025-10-13T13:10:02.576Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>YTg2MWYxNTktMTEyNi00YWYxLWI4MmMtNzBlODk1NDQwMjE3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HYICEAM_GE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Recusada</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>RAFAEL BARBOZA</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>NzE0ZTQzMTctOWNiOC00OTI2LTgyOTItOWY5NzYxZDE3OGQxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OWRkYjhiMjgtNzQ5NC00NzE5LWI5OTctM2VmYmVlZGNjNDU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RJJ9H2YGWG</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Maquina 02</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Referente orçamento : NRLO2Z0E0001 TERRAFORM 5KG RECICLADORA DE RESIDUOS ORGANICOS DATA DE COMPRA 13/01/2023</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>451.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>451.5</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2025-12-19T16:01:13.514Z</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2025-12-12T16:02:27.309Z</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>MzMxMDI2Nzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>ZWFiZTI5NDgtMzY0Ny00ODVkLThmNjEtODhjMGI2N2Q4Nzk2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>ZmU4N2U3MGQtMzJiMi00MDhlLTljNzktZTRmN2M1ZDcyNzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>YTA2ODQ4YTYtZjMxNS00NGJmLTkwMmYtNWI0MGRlYzQ1NTIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>R1O0SXDSWG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CONVERSÃO DO EQUIPAMENTO - SECRETARIA DE AGRICULTURA E ABASTECIMENTO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Orçamento para fazermos a conversão de 380v para 220v</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-01-23T17:25:57.681Z</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-01-16T17:30:58.730Z</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>NDgyNTk1Mzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>MzMzMDQ3ZTYtMzU1OC00MTZjLWExZGYtNWU4MTg4ZmY2YzdhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HJE6OUN5LE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bayer Uberlandia</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico do  tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo do  nitrogenio que vai utlizado + laudo de garrafa  maçarico e caneta (laudo )  para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo nitrogenio, maçarico (laudo da garrafa) e caneta para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
+        </is>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2025-09-09T13:53:17.012Z</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>NTU4NTRiMjItMTA0Yi00ZDEzLThiMDktNzdjYzcxMTFmNzU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BYOHBAHQXX</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5996.77</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5996.77</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2025-09-15T21:48:09.008Z</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>OTNhMDBkOGItMzEyYy00MzVkLTlmYzItY2I4NWU2ZTQ5MzU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BKODRN5YZX</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Autorizado por João</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2025-11-13T15:27:36.746Z</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2025-11-06T15:27:46.917Z</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>YzQ4ZWViOTctYjVjYi00Y2ZjLTgxZmItYjI4NDEzNzdiMDBlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RYKLTHHLWL</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sobrecarga no motor - 03262073000140 - RCR REPRESENTAÇÕES E SERVIÇOS LTDA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sobrecarga no motor e resíduo empedrado</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-02-02T19:59:46.198Z</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Lucas Uenishi Tada</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-01-26T20:04:54.521Z</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>MzQwMzM1ODo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>ZjUzOGNhMTktYmI4Yi00MmUwLTk4ZDYtYzQyNzk3M2U2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SYSJ0HARXL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2123.15</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2123.15</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2025-11-04T13:33:37.491Z</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2025-10-28T14:06:21.222Z</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>MjIwOTU3OGEtZGZlNi00Njk1LThhZWQtNjM5YzVjZjJmZTg5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SJH_RHL1BL</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>511.65999999999997</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>511.65999999999997</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2025-11-10T14:43:09.194Z</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Viktor Chagas</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2025-11-03T15:08:36.141Z</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>MzkzMzA3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>ZmU3NjFlZTktOWMxMy00OWM5LTlkZWItZjU0NGMzZjM3YTBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Y2ZiMTU2NjUtYjVjMS00ZmZmLThkNTYtZjY3ODU0ZmVlNDUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HJT5WSB8BE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Vazamento de óleo por baixo da máquina - 50122571000177 - PREFEITURA DO MUNICÍPIO DE ITATIBA.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Vazamento de óleo e troca de peças</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cancelada</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-02-02T19:52:49.086Z</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-01-27T12:28:33.000Z</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-01-27T12:28:33.000Z</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Lucas Uenishi Tada</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-01-26T19:59:17.023Z</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>MzM3ODQxNDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>MTZkNGJlZmQtNjNlNC00MWQ1LWEzNTEtODYxOWM3N2JmMzQ3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ZGQ4ZDMyMzQtMGY3ZC00ZmQ4LWIwMTAtMDc0NDVjZWQ2ODY2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RJA9B33WZG</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>90400888000142 - BANCO SANTANDER (BRASIL) S/A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>REFERENTE A VISITA TECNICA PARA DIAGNOSTICO 
+O VALOR PODE SER ALTERADO CASO PRECISE DE MAIS TEMPO PARA MANUNTENÇAO
+PEÇAS NAO ESTAO INCLUSAS NESTE ORÇAMENTO , CASO SEJA NECESSARIO, SERA ADICIONADO NO VALOR FINAL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2025-12-09T18:46:05.954Z</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2025-12-02T18:53:10.136Z</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>MzMzMDQ1Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SYSDANQY-X</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MAQUINA 02</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Autorizado por João</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>979.73</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>979.73</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2025-11-13T15:27:16.361Z</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2025-11-06T15:27:31.134Z</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RYW5U8N7WG</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>90400888000142 - BANCO SANTANDER AMADOR BUENO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Referente orçamento Santander Amando Bueno</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1224.475</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1224.475</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-01-02T18:34:01.969Z</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2025-12-26T18:48:40.881Z</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>MzMzMDQ1Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SK1FN_56XX</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1172.55</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1172.55</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2025-10-20T12:26:24.223Z</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2025-10-13T12:45:43.188Z</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>MzQ2NDM2Nzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>ZjQzMjRhOTEtZWM2NC00ZWUzLWFmNWItODM5NDliOWM2MjkzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RY0PVITH-L</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Manutenção dobradiça 02.042.860.0001-13</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Referente a manutenção da dobradiça  da redutora</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>850.76</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>850.76</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Cancelada</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-01-27T19:00:18.732Z</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-01-20T19:19:25.000Z</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-01-20T19:19:25.000Z</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Lucas Uenishi Tada</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-01-20T19:17:25.784Z</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>NDM1ODE3Nzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ZTU2NGM3MmYtMGI2My00NGQ4LWJhZDYtYWEwNWQyMjk1OGI0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>R1MXL4RSBG</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>60580263000149 - ALBANY INTERN FELTROS TELAS INDUSTRIAIS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>cliente solicita orçamento da peça</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-01-21T15:16:56.016Z</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-01-14T15:28:26.334Z</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>NmQyZWFkMDctOWI5NC00YjQxLTgyZjYtN2VjYTAyYzM5ZTFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>NDgzNTU3MTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Zjk2NjZmMDUtZjI0Ny00MTQxLWJmMmItMzZhOWRkNzNlYzgwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H16WCCZPEG</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FRANCESCO DE TOMMASO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2025-10-14T18:12:15.015Z</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BYDFGIWKZG</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>40.894999999999996</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>40.894999999999996</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-11-11T15:57:22.457Z</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Marcos</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/e9de7ba0-386a-464d-8581-a8798001ad78/signatures/a05c1641-9b6c-465a-90ae-a4510b4e3986.png</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2025-11-04T15:57:50.841Z</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>YTg2MWYxNTktMTEyNi00YWYxLWI4MmMtNzBlODk1NDQwMjE3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2025-09-29T20:26:53.403Z</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>NDgyNTE1Mzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>MTcwZjFjYjQtMmE0OC00ZTYyLTg4ODAtZjBlOGU3M2I1MmExOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ZWVmYjYzNGEtMzg5YS00YjU3LTg5ZjQtYjQ0NDEwZmNlOTlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H1HFJ_C8ZL</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>40240521000130 - RAVELY - SERVICOS ADMINISTRATIVOS S A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>40240521000130 - RAVELY - SERVICOS ADMINISTRATIVOS S A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-02-06T18:27:35.984Z</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-01-30T18:40:19.770Z</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>MDU1N2Q3Y2ItZmMxYi00OGVhLThkNDUtNzE5OGI0YjUwMWJkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>NDM1ODE5OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>NzYwMWZlNDAtMzg2Mi00YjcyLTgwYWEtYzdkNWM1YmZiYmZjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BYM4IOEEBX</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2123.15</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2123.15</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2025-11-18T12:23:08.942Z</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2025-11-11T12:25:14.798Z</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>MjIwOTU3OGEtZGZlNi00Njk1LThhZWQtNjM5YzVjZjJmZTg5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BYNKSGREBL</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>03262073000140 - RCR REPRESENTAÇÕES E SERVIÇOS LTDA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>956.025</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>956.025</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2025-11-21T18:23:47.104Z</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Débora Mendes Mangaba</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/fbbec352-79e6-41e3-9553-a70ca4dd9b61/signatures/e629a18e-6cbe-4b79-8890-7071450b92a9.png</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2025-11-14T18:28:52.343Z</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>ZWI1NTJkMzAtNjEwMS00NjM1LWE5MzYtOWE2ZTAwYjY2ZjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>MzQwMzM1ODo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>ZjUzOGNhMTktYmI4Yi00MmUwLTk4ZDYtYzQyNzk3M2U2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ZmUxZjQ1MjItOTlmZi00OTgyLTg5MTctNWEzYjAyZTkzODIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>R1GRNINMWL</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>90400888249086 - BANCO SANTANDER INTERLAGOS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Orçamento na unidade de Interlagos, lembrando que e troca de peças e nao preventiva</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1197.8</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1197.8</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-01-02T18:19:58.819Z</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2025-12-26T18:30:18.349Z</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>NDU4ZDY0OTgtYjQwNy00MTdhLWE5YjYtNTg5ZDcyNGExMTQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>NTE2MTc5NTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>ZTRkNTk4YzgtZTAxMi00ZWVkLWJkZTgtYTBkMjEzYmNkZjFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3273,7 +6401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7416,6 +10544,5252 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ZDU3OGQ2MTktZGJkYy00YjEyLTkzMzItNTExYTlkYjlkZTVmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>12525</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="n">
+        <v>10</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>NTViMThiNzUtNWVmNy00ZDU1LWIxNzMtOGY5NjZhYTE4ZWMwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>12525</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>350</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="n">
+        <v>6</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>350</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="n">
+        <v>6</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>7375</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="n">
+        <v>6</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>7375</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>375</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="n">
+        <v>6</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>375</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>680</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>680</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>855</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>855</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>NWU1NmZlZjUtMjlkZi00OGVkLWIyNWYtMWY0MDU0MzU5YzM3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>660525</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ODBiZWNhYTUtOGMwYS00OGM1LWI4MGQtYjZhYzUyNzk3ZDg2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>660525</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>ODBiZWNhYTUtOGMwYS00OGM1LWI4MGQtYjZhYzUyNzk3ZDg2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ZTUyMzVkODgtOWEyYi00ZmI5LWE4ZDAtMTg4NDc0MWY1YzNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>350</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>OGFmODc0N2UtMGFlMy00NjU1LWE5NTctY2RiZGU4NDljYjAxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>350</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>OGFmODc0N2UtMGFlMy00NjU1LWE5NTctY2RiZGU4NDljYjAxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="n">
+        <v>43</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>43</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>85</v>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>85</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>350</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>350</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>9</v>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="n">
+        <v>10</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>9</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="n">
+        <v>6325</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>6325</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>375</v>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="n">
+        <v>10</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>375</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="n">
+        <v>350</v>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="n">
+        <v>10</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>350</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="n">
+        <v>2502</v>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="n">
+        <v>10</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>2502</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="n">
+        <v>10</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="n">
+        <v>85</v>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>10</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>85</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" t="n">
+        <v>700</v>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>10</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>350</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>680</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>680</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="n">
+        <v>855</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>855</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" t="n">
+        <v>96</v>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="n">
+        <v>6</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>48</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="n">
+        <v>6</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="n">
+        <v>6</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="n">
+        <v>6</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="n">
+        <v>6</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MjQwOWM1YjItZGNmYi00MGM3LTk2MGYtNzJhZmU1YjI0ZGE3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="n">
+        <v>350</v>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>OWRkYjhiMjgtNzQ5NC00NzE5LWI5OTctM2VmYmVlZGNjNDU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>350</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>OWRkYjhiMjgtNzQ5NC00NzE5LWI5OTctM2VmYmVlZGNjNDU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NDE1ZjIwZDEtYTAzMy00OThmLWJmNTYtNTk0YWJjNzcwYjBiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="n">
+        <v>165</v>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="n">
+        <v>4</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>OWRkYjhiMjgtNzQ5NC00NzE5LWI5OTctM2VmYmVlZGNjNDU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>NWMyNzRkMGItZTBmMy00ZDU1LTljNTAtMDBmYTFlYTdlZmUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>165</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>OWRkYjhiMjgtNzQ5NC00NzE5LWI5OTctM2VmYmVlZGNjNDU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ZmJlY2M1NzUtMTYzMC00ZGIzLWJiYmYtYTU0Y2EyMDM2MmQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="n">
+        <v>85</v>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="n">
+        <v>4</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>OWRkYjhiMjgtNzQ5NC00NzE5LWI5OTctM2VmYmVlZGNjNDU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>85</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>OWRkYjhiMjgtNzQ5NC00NzE5LWI5OTctM2VmYmVlZGNjNDU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ZmExODBlYTMtZTVlNC00YjJiLWIxZDQtOGYyYjk5ZDY1YTc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>YTA2ODQ4YTYtZjMxNS00NGJmLTkwMmYtNWI0MGRlYzQ1NTIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>YTA2ODQ4YTYtZjMxNS00NGJmLTkwMmYtNWI0MGRlYzQ1NTIxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo nitrogenio, maçarico (laudo da garrafa) e caneta para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>494677</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
+B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
+B527034 - MANTA ISOL FIBRA CERAMICA  ALUM 3810X610X38MM 2.32 M³ P/ROLO Qtd = 0,2 M2
+B538109 - TERMINAL C/ ISOLACAO CABO 1,5 - 2,5MM OLHAL AZUL TP2,5-4 - INTELLI Qtd = 6 PC
+B538119 - LUVA C/ ISOLACAO CABO 1,5 / 2,5 (EMENDA AZUL) INTELLI LEP-22 Qtd = 2 PC
+B538121 - CONJ.TERMOSTATO CAEM TU HC 120°C 30A 5MMX080MM 980MM 3/8CBP Qtd = 1 PC
+B538233 - INTERRUPTOR DE TECLA MARGIRUS 30223 M2FT1DE3Q/197 BIP. 10A VERDE Qtd = 1 PC
+B538345 - CABO ELETRICO FLEX. 1,5MM SILICONE C/ FIBRA DE VIDRO 200º Qtd = 2 MT
+B538683 - CABO PP C/PLUG CABO INJETADO 90º10A(3.0X1.5X2000MM) Qtd = 1 PC
+B538806 - TERMINAL DE ENCAIXE FEMEA "FASTON" C/ ISOL. (AZUL 1,5 - 2,5MM) Qtd = 4 PC
+B538A84 - PRENSA CABO BSP 1/2 LP+P/UV-LT-PA-40 DAN KRAUS MULLER Qtd = 1 PC
+B538I97 - ESPELHO PLASTICO CAEM PRETO Qtd = 1 PC
+B546053 - MICROVENT. LINEAR 110/220V 60HZ MOD. MINILINE Qtd = 1 PC
+B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>494677</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="n">
+        <v>6</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="n">
+        <v>375</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="n">
+        <v>6</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>375</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="n">
+        <v>7375</v>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="n">
+        <v>6</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>7375</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>YjljMTRhODUtYzlmZC00ZjBhLWExZjMtYmExMTY2YzMzZWFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="n">
+        <v>350</v>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>6</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>350</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ZWM2ZTEzNTktN2U5My00MjJiLWEwNmYtZmQ3ZTIxNTg1ZWNhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>6</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>NDJiOTgzOTEtYzhmOS00MmU2LWJkNzItYjdkYzM4MDIyMDY1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="n">
+        <v>350</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>3</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>YzQ4ZWViOTctYjVjYi00Y2ZjLTgxZmItYjI4NDEzNzdiMDBlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>350</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>YzQ4ZWViOTctYjVjYi00Y2ZjLTgxZmItYjI4NDEzNzdiMDBlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ODEyNGM5NTAtZGU4ZS00Yjc4LTgyZDktZTFlM2U5YWU0ZWRkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>39</v>
+      </c>
+      <c r="C147" t="n">
+        <v>78</v>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="n">
+        <v>3</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>YzQ4ZWViOTctYjVjYi00Y2ZjLTgxZmItYjI4NDEzNzdiMDBlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>2</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>YzQ4ZWViOTctYjVjYi00Y2ZjLTgxZmItYjI4NDEzNzdiMDBlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3.2215e+16</v>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>5</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>3.2215e+16</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="n">
+        <v>823</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>310Km</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>5</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>2</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>70</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Enviado por Sedex10 de SP para DF</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>43</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="n">
+        <v>908</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>5</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>350</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="n">
+        <v>16</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="n">
+        <v>16</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="n">
+        <v>117</v>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>16</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>117</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3</v>
+      </c>
+      <c r="C155" t="n">
+        <v>9000000000000001</v>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="n">
+        <v>16</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="n">
+        <v>825</v>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="n">
+        <v>16</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>825</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="n">
+        <v>717</v>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>16</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>717</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7375</v>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="n">
+        <v>16</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>7375</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" t="n">
+        <v>96</v>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="n">
+        <v>16</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>48</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="n">
+        <v>43</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Troca do Balde via correio</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>16</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>43</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3.33e+16</v>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="n">
+        <v>16</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>1.11e+16</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>YWVhMDUwNDEtMWZjMy00MGY0LTliMjEtZmQ0Njc2ZmYxMmRiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="n">
+        <v>16</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>YTI5MDAxYjctNzYxNS00Yzc0LTk1MWItYWJjMDg5NWJiN2QzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>2525</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>YzczZTA5NTktMzAzNS00NWE1LWJiYWUtNWQ5YWYzOTcwOTYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>9</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1.89e+16</v>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="n">
+        <v>16</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ZDk0OTlmM2UtNGFlYy00MzM3LWFiY2UtYzRmMjBhYjFiN2ZiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="n">
+        <v>16</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ZDk1OWFkMjYtZGJkZi00OWRkLWI5ZTktMjJiOTZlN2VlYzBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1.26e+16</v>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="n">
+        <v>16</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>4.2e+16</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ZTk0MDQ3MTktYzcwMy00ZTU5LTg5MjMtOGU3MDllYTg0MjAyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="n">
+        <v>16</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Y2U0YmMxMGItMGE2Yi00MmI0LWFkZWMtNmM1MzYwNjc3MzI3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>101</v>
+      </c>
+      <c r="C167" t="n">
+        <v>202</v>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="n">
+        <v>3</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Y2ZiMTU2NjUtYjVjMS00ZmZmLThkNTYtZjY3ODU0ZmVlNDUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>2</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Y2ZiMTU2NjUtYjVjMS00ZmZmLThkNTYtZjY3ODU0ZmVlNDUxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Y2VmZjBmYzAtNGE0MS00MDQzLWI1MGYtMzZkMDkyMDVjYjdhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="n">
+        <v>350</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>3</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Y2ZiMTU2NjUtYjVjMS00ZmZmLThkNTYtZjY3ODU0ZmVlNDUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>350</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Y2ZiMTU2NjUtYjVjMS00ZmZmLThkNTYtZjY3ODU0ZmVlNDUxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MWUzZTY3NzAtNzVkZC00NmU3LWExZGQtNDM5ZjQ5NGYwYjZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="n">
+        <v>350</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ZGQ4ZDMyMzQtMGY3ZC00ZmQ4LWIwMTAtMDc0NDVjZWQ2ODY2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>350</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>ZGQ4ZDMyMzQtMGY3ZC00ZmQ4LWIwMTAtMDc0NDVjZWQ2ODY2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Mzc5OGE1YjEtNjljYy00ZjY2LTg0Y2EtOWI1MDhiMGI5ZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="n">
+        <v>375</v>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="n">
+        <v>7</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>375</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>NDVkYzYzNDctNTg3YS00OWE4LTkwNDUtMTg5ODRhZDI4MzUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="n">
+        <v>350</v>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="n">
+        <v>7</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>350</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>NGJkNjVmOTAtODM1NC00ODI2LWJjZmUtMTBjNzMwNTllNzgwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="n">
+        <v>7</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OTQ5YzlkZDctYzczOC00ZjM5LTliNjUtMDQ2MGZkNjM4ZjQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="n">
+        <v>85</v>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="n">
+        <v>7</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>85</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>YWU0MjBjOTYtYjVhMy00MmVmLTk1MmUtNWRlZDkxMWY1Mjk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="n">
+        <v>350</v>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="n">
+        <v>7</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>350</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ZGU2MDQ1ZGUtMmJlYi00NzE5LWJlNjAtZTM5YzczOTAzMzI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="n">
+        <v>7</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>1365</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>ZGRmY2QxZDAtZjYzZi00NmNiLWFjZDItZjVmOTU0MGU3NmIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MjY4NWQxYmEtYjg5My00NzM0LWJjOGQtMWI1OTQ4ZDJhMzJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1225</v>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="n">
+        <v>7</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ZDM1MmRmY2UtNTk2NC00Nzk1LTgzZDEtMTIxZDI0ZmI3MjkyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>1225</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>M2UwOGU4NTMtMjViMy00MTUzLTg0N2UtNGJiMDE2NGViMTExOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.7985e+16</v>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="n">
+        <v>7</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>YjVlY2ViMDctYjBmZS00NTM1LWI2MmEtNDVhNWIyNzA0MTNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>29975</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>NWIxMTQ2NTEtOTg3MS00MDVmLTk0ZGUtNmQ3MDk2OGZiNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="n">
+        <v>240</v>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="n">
+        <v>7</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>NjUyN2M5NDUtNzJkNi00NTYxLTg2NGItYmM2MGU5OGExZDljOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>240</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ODQ0MDI2ZDgtMGY3YS00OTc3LWIxNDMtM2MzNGU5MGUyYzU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="n">
+        <v>350</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>7</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>350</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>YTFjNzQ1MTYtYTljMS00M2I3LTk0ZjItMGU5MDg5ZWQ3N2ZhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>2</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="n">
+        <v>7</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>NTAzNjBhYjMtZTdhZC00NmIwLWFiNjYtMWJhNzZlNDgwMTFhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>6325</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ZjVkOTQ0YTAtMzViYy00YmM0LWIyODAtNjA3MjQyZDMzMzFhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="n">
+        <v>205625</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2,25 metros ( a mesma encontra se rasgada)</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>7</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>OGMwNDI0MDgtYTBiNS00NTVkLTg5NWQtNTViYTRjMmZkYTRlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>205625</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>ZTIxYTk1NDctZjk1OC00NGFiLWE0MmUtN2IxYzYzYzRiZWMyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>3</v>
+      </c>
+      <c r="C182" t="n">
+        <v>99</v>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="n">
+        <v>6</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>33</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="n">
+        <v>38656</v>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="n">
+        <v>6</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>350</v>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="n">
+        <v>6</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>350</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="n">
+        <v>85</v>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="n">
+        <v>6</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>85</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>350</v>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="n">
+        <v>6</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>350</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MGY5OGFlZjAtY2NjYS00MTI4LTk0MWYtOWVjNDE1ZjYwMWU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>2</v>
+      </c>
+      <c r="C187" t="n">
+        <v>935</v>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="n">
+        <v>6</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>YjBiMDlkNmYtNGJmOS00NDEzLWE2N2QtM2JiNjY4MDk2ZmViOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>4675</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>NzBhYzVhYmYtYzNjMC00M2Y0LTkzOTgtZjAwMTQ3NTlkMzg0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>162</v>
+      </c>
+      <c r="C188" t="n">
+        <v>324</v>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="n">
+        <v>6</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>OTBiYWMzMzgtOTc0YS00ZjkxLWEyMGItODQ5ZGMzYTNhOTdmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="n">
+        <v>350</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>350</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Y2UwM2M2OGQtNzU0ZS00ZjFjLWFhOTQtNzc4ZGY4NzcyNWRiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>6325</v>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="n">
+        <v>6</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>NTAzNjBhYjMtZTdhZC00NmIwLWFiNjYtMWJhNzZlNDgwMTFhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>6325</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ZjdmNDIxOTktNDEwNy00NjdjLTg0NWMtNGQ1M2RlYmI4YjYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2.001e+16</v>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="n">
+        <v>6</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>MTY1NGI0N2YtMTZmZS00OTljLWJhYTItYjk1ZDVkNjgwMDE4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>2.001e+16</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>ZTQ3NWI1NDgtNGI0ZS00MjI4LTgyZGEtNmI3N2M4OWIwYjIyOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>M2Y5ZjYyN2UtZTk0MC00ZjgyLTgxMWUtZTA5ZDBjMmE5Yzg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="n">
+        <v>43</v>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="n">
+        <v>3</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>ZTU2NGM3MmYtMGI2My00NGQ4LWJhZDYtYWEwNWQyMjk1OGI0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>43</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>ZTU2NGM3MmYtMGI2My00NGQ4LWJhZDYtYWEwNWQyMjk1OGI0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>NDY1MzAyNmUtNmVlZi00ODk2LTk0MTAtY2MzZjViNTkyMDFhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="n">
+        <v>640</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>B538J73 - CONTROLADORA  WR133E 12/24V FULL GAUGE  VER.01 REDUT. RESIDUOS</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>3</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>ZTU2NGM3MmYtMGI2My00NGQ4LWJhZDYtYWEwNWQyMjk1OGI0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>NTI0MWRiMjMtNWFhNy00ZmNhLTgzMzMtZDlmNzU2NmU1YWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>640</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>ZTU2NGM3MmYtMGI2My00NGQ4LWJhZDYtYWEwNWQyMjk1OGI0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="n">
+        <v>8</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>1086</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="n">
+        <v>350</v>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="n">
+        <v>8</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>350</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="n">
+        <v>8</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3795</v>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="n">
+        <v>8</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>3795</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="n">
+        <v>350</v>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="n">
+        <v>8</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>350</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="n">
+        <v>8</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>8</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1.68e+16</v>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="n">
+        <v>8</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>MzA4MjgxOWUtMzhjMi00NjI1LTllYjctZDU2ZjU3ZTM0YjQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="n">
+        <v>6</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>M2E3MTI4ZDUtMzdkNi00MzMyLWFhYTAtZmFhMGUxZmRhODQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="n">
+        <v>6</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ODNiYTk3NjQtZDk5Yy00NzY3LTlkZGYtM2E4NTUyZDk5Y2MyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" t="n">
+        <v>96</v>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="n">
+        <v>6</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>48</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>OGM1MGMxOWYtZDViMy00ZDhjLTlkNjItYjlkM2ZkYzg3MmRlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="n">
+        <v>6</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>YjE1ZmYzNmMtMGYyYy00NGVhLWE2ZDQtM2M4ODUwNzY5ZDNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="n">
+        <v>6</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="n">
+        <v>43</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>13</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>43</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3325</v>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="n">
+        <v>13</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>3325</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="n">
+        <v>717</v>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="n">
+        <v>13</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>717</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>7375</v>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="n">
+        <v>13</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>7375</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>117</v>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="n">
+        <v>13</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>117</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="n">
+        <v>4.2e+16</v>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="n">
+        <v>13</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>4.2e+16</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="n">
+        <v>13</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>48</v>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="n">
+        <v>13</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>48</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="n">
+        <v>475</v>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="n">
+        <v>13</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>475</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="n">
+        <v>13</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="n">
+        <v>13</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="n">
+        <v>13</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>MjE1NmJiODMtMGVlMC00MjdiLTk5OWUtODNhNzlhMmU1Y2ZhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Incluso:
+- Manutenção preventiva e limpeza em fornalha e dutos (Bimestral)
+- Mantenção preventiva no exaustor (Trimestral)</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>2</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>ZWVmYjYzNGEtMzg5YS00YjU3LTg5ZjQtYjQ0NDEwZmNlOTlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>OTk1MjQ1MDktZjcyZi00YWVkLTgxMmMtNTQ5YzQzZWJiODg4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>ZWVmYjYzNGEtMzg5YS00YjU3LTg5ZjQtYjQ0NDEwZmNlOTlhOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>M2IyYWRjNTktYzQzMS00NTYzLTkyNjItYjdmNzU4MDY4M2FjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" t="n">
+        <v>823</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>310Km</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>5</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>2</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>OWEyZWU0YmUtMTRkOC00MzI1LWJiYTItNWZjNzdiNTQ5MzBiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" t="n">
+        <v>908</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>5</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>350</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>YTA3NmI4ZmQtODU4OS00MmNlLThkZTUtYWVjMDg4MWU4ZjkxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="n">
+        <v>70</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Enviado por Sedex10 de SP para DF</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>43</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ZTYxOTZmZjktMGI5Ni00NDlkLTkyY2EtNDJkNTgzZmFlODFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.2215e+16</v>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="n">
+        <v>5</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>3.2215e+16</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>ZjU4YWM1ZjYtNWE5OS00NjJhLThmOTctNmZjNjJlYjgwNWNjOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>MTI0MGFkOTEtNTdkZi00MjUwLTliOTUtMzJiMzU2MzBlYTgxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" t="n">
+        <v>350</v>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="n">
+        <v>5</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>350</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>OGQwY2NlYzQtZjdlNy00YTk1LWJhNzYtNTI5NjM1MDkzZWU1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" t="n">
+        <v>2739</v>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="n">
+        <v>5</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>OTM3NDhlODMtNzUwMy00ZDc3LWEwYWUtZmE5MTU2YzY1MzMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>2739</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>YjU3Y2ZhN2QtNTQ2MS00N2M2LTkyNzktMzc2MTM3ZTljNDg5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" t="n">
+        <v>205625</v>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="n">
+        <v>5</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>OGMwNDI0MDgtYTBiNS00NTVkLTg5NWQtNTViYTRjMmZkYTRlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>205625</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ZDkyZjAzMWQtMDAwZS00ZDVkLTgyZjctYmRjOTgyMWFkZGQ3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>2</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="n">
+        <v>5</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>NTAzNjBhYjMtZTdhZC00NmIwLWFiNjYtMWJhNzZlNDgwMTFhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>6325</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>ZmJiZWMzNTItNzllNi00MWUzLTk1NTMtYTcwY2E0ZGQ5YjYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>MmY0Nzg2OGYtMWRhNi00NWQzLTg0ZTAtMWU5ZTkzYWUxODg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>2</v>
+      </c>
+      <c r="C227" t="n">
+        <v>5478</v>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="n">
+        <v>4</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>ZmUxZjQ1MjItOTlmZi00OTgyLTg5MTctNWEzYjAyZTkzODIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>OTM3NDhlODMtNzUwMy00ZDc3LWEwYWUtZmE5MTU2YzY1MzMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>2739</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>ZmUxZjQ1MjItOTlmZi00OTgyLTg5MTctNWEzYjAyZTkzODIzOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>YWM4YmE3ZDktOGY2MC00MzM0LTgyOGMtZWQyNWRiZTMzMThkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>6</v>
+      </c>
+      <c r="C228" t="n">
+        <v>300</v>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="n">
+        <v>4</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ZmUxZjQ1MjItOTlmZi00OTgyLTg5MTctNWEzYjAyZTkzODIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>ZjVhYTQ0MzAtYTIxMi00NTA5LWJhMWItNzc5YTk5OGRhYjQxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>50</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>ZmUxZjQ1MjItOTlmZi00OTgyLTg5MTctNWEzYjAyZTkzODIzOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ZDY4NjM2MDAtOTMzNS00NzY5LTgzNzItZDhlZTY5ZDM3ZTc2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" t="n">
+        <v>350</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>4</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>ZmUxZjQ1MjItOTlmZi00OTgyLTg5MTctNWEzYjAyZTkzODIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>350</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>ZmUxZjQ1MjItOTlmZi00OTgyLTg5MTctNWEzYjAyZTkzODIzOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,75 +472,80 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>currencySymbol</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>expiredAt</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>refusedAt</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>canceledAt</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>approvedBy</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>createdBy</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>approvedSignature</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>order.id</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>discount.type</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>discount.value</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>discount.total</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>customer.id</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>location.id</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>status_original</t>
         </is>
@@ -612,61 +617,62 @@
           <t>4000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2025-11-18T15:58:38.481Z</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2025-11-11T16:06:07.949Z</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>NTYyNjA5ODctODA0MS00ODJlLWE1MTQtOTY0ZTQyZWRjOTYwOjU3MDE2</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>NDgyMzQxODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>NmFiMDUyZTMtMmRkMi00NWYwLWI1YzAtNzI5N2NmMGJiMzZhOjU3MDE2</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -703,69 +709,70 @@
           <t>964.85</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2025-11-18T15:45:15.510Z</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Edina K O Mishima</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/1774f003-3175-4be8-801c-c7e958af19a8/signatures/650d7c22-e91c-4757-9ac9-9ad5beab0def.png</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2025-11-11T15:48:38.327Z</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>OTRkZmU3YjYtNDc4OC00OWJlLTk2OWMtYmQ5Y2Q4ZWRiMTY3OjU3MDE2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>NDgzNDgwNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>NGNlYTU1YmYtMjg4My00OWI2LWE5YjEtNGEzNTNmZWU3MzZhOjU3MDE2</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -806,61 +813,62 @@
           <t>1056.4</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2025-11-12T12:52:46.887Z</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2025-11-05T13:06:35.085Z</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>ZWMwNWE3NTgtODkyOC00ZjE5LWI0YTgtYjY0NmYwMDY2OGIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>NDE2MTc1Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>ZDg5NzUyMzktNDc5NS00NDU2LTg0MmItMjZhZjE2MWI3MWUzOjU3MDE2</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -897,61 +905,62 @@
           <t>660.525</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2025-12-18T21:29:48.068Z</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2025-12-11T21:29:54.203Z</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>ZjZiNTJjY2UtNDFhMS00NjllLTkyNDEtMjIzYmY5ODE2NmJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -992,57 +1001,58 @@
           <t>850.76</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-02-06T18:45:20.986Z</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2026-01-30T18:45:35.907Z</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1083,65 +1093,66 @@
           <t>350</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Cancelada</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-01-29T14:37:35.560Z</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-01-22T14:57:37.000Z</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-01-22T14:57:37.000Z</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2026-01-22T14:40:07.831Z</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>YmEwMmQ1NzItYmIwMi00NTAxLWI4NWYtYmZiODY3NjIwZmRhOjU3MDE2</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -1178,61 +1189,62 @@
           <t>300</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2024-08-14T17:42:21.925Z</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>IRACILDA LOPES</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2024-08-07T17:45:02.123Z</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>MDIzNDM2N2QtZGJmOS00YjhlLTk2ZjUtZWE2N2NlMGVhYjljOjU3MDE2</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1273,65 +1285,66 @@
           <t>1535</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2025-09-04T15:24:13.519Z</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Rafael Machado Barboza</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2025-08-28T15:35:41.479Z</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1376,61 +1389,62 @@
           <t>988.85</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2025-12-09T21:20:29.860Z</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2025-12-02T21:20:54.686Z</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1467,61 +1481,62 @@
           <t>530.25</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2025-10-09T21:18:04.630Z</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2025-10-02T21:19:25.794Z</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>MzQwNDRlN2UtMzgxYi00Nzc5LTk1MGItYTY3ODczZDg4NWM0OjU3MDE2</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1562,57 +1577,58 @@
           <t>850.76</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-01-27T19:18:07.101Z</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>2026-01-20T19:19:08.741Z</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1657,69 +1673,70 @@
           <t>2167.29</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2025-10-06T13:42:48.402Z</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">Joana D’Arc Oliveira </t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>MjU3OWZlNzYtYWVlNC00ODU0LWEyYTUtNDdkMWI2ZGY5ZDlmOjU3MDE2</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1756,61 +1773,62 @@
           <t>979.73</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2025-10-06T18:41:42.725Z</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1847,61 +1865,62 @@
           <t>1298.9</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2025-10-06T18:34:31.188Z</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>2025-09-29T18:38:37.635Z</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1938,61 +1957,62 @@
           <t>4984</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2025-10-15T21:09:42.233Z</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>2025-10-08T21:12:33.362Z</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>NDgzNDc2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>ZThkYWNiNmItMDliOS00Y2Y0LTgyNjgtOGU5OTk4NzQ3MmNkOjU3MDE2</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2034,61 +2054,62 @@
           <t>1016.75</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2025-12-19T15:56:33.655Z</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>2025-12-12T16:00:42.963Z</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>MzMxMDI2Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>ZWFiZTI5NDgtMzY0Ny00ODVkLThmNjEtODhjMGI2N2Q4Nzk2OjU3MDE2</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2131,61 +2152,62 @@
           <t>350</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2025-12-24T21:32:57.350Z</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>2025-12-17T21:33:20.182Z</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2222,61 +2244,62 @@
           <t>660.525</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2025-11-14T16:10:10.258Z</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>2025-11-07T16:26:09.914Z</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>ZjZiNTJjY2UtNDFhMS00NjllLTkyNDEtMjIzYmY5ODE2NmJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2317,61 +2340,62 @@
           <t>138.57999999999998</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>2025-12-15T20:05:35.735Z</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>2025-12-08T20:11:36.676Z</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>M2EzOTI5YTItODc3Zi00NTJlLTk1NDktMmU5YWRiMWMwZmQ1OjU3MDE2</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>NDgzNTU4Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>NTk1Y2ZkMTYtMTk4YS00OTE4LWI5YzMtZjcwMTliOTdlNDVjOjU3MDE2</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2416,61 +2440,62 @@
           <t>530.25</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>2025-10-17T12:48:39.389Z</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>2025-10-10T13:07:18.487Z</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>NDgyMzMyODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>NTg2M2M0ZTEtMThhNC00Y2YyLWFhNDktYTViMTdhYzE0MmZmOjU3MDE2</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2515,65 +2540,66 @@
           <t>1047.65</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Recusada</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>2025-11-24T15:13:20.559Z</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>2025-11-24T14:45:19.000Z</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>2025-11-17T15:14:20.735Z</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>refused</t>
         </is>
@@ -2615,61 +2641,62 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>2025-11-25T21:47:25.554Z</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>2025-11-18T21:53:35.934Z</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>NjYwZjY1NTAtNjFmZS00N2NmLTlmZTktMzY2ZWVjNmViZGJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>NTgwMDkyOTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>YTg3MTBjZDAtMzUwOC00OWNmLWIwMTAtMzMwNGVkOTA5ZWI0OjU3MDE2</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2722,57 +2749,58 @@
           <t>1700</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>NTU4NTRiMjItMTA0Yi00ZDEzLThiMDktNzdjYzcxMTFmNzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2817,57 +2845,58 @@
           <t>47370</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>RAFAEL BARBOZA</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>2025-08-08T18:27:17.728Z</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>NzE0ZTQzMTctOWNiOC00OTI2LTgyOTItOWY5NzYxZDE3OGQxOjU3MDE2</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2913,61 +2942,62 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>2025-12-16T20:19:12.508Z</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>2025-12-09T20:21:45.714Z</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>MzIyOGRmMDAtMThlNi00NTc3LTk2MzctYmVjM2QxYmZlOWYwOjU3MDE2</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>NTg1NDM3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>M2NhMmM5M2MtNWIwNi00OWQwLWFmODgtYTQzNmJiOTUyM2EzOjU3MDE2</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3008,65 +3038,66 @@
           <t>484</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>2025-12-08T12:21:25.404Z</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>douglas simao</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>2025-12-01T12:28:02.404Z</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>NDUwNzM2Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>ZjBjMzdjOTgtNWY3Yi00ZGQ5LTgwNTktMDZkMjI4YTAzYTAwOjU3MDE2</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3107,61 +3138,62 @@
           <t>5996.77</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>OTNhMDBkOGItMzEyYy00MzVkLTlmYzItY2I4NWU2ZTQ5MzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3202,61 +3234,62 @@
           <t>1756.6</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>2025-12-11T14:05:43.837Z</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>2025-12-04T15:21:12.082Z</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Y2NjZDRjMTgtOWYwOC00YjUwLWFiNzktOGU0NGNhZTQzMTg3OjU3MDE2</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>MzUzMTEwNTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>NTM2Nzc5ZjUtZjA3MS00NzY0LTkyNmMtNzQwNmNlZDgzZjEwOjU3MDE2</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3293,61 +3326,62 @@
           <t>490.38</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>2025-09-29T18:44:47.397Z</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3392,57 +3426,58 @@
           <t>1535</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3483,57 +3518,58 @@
           <t>660.525</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>2026-01-29T17:13:31.699Z</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>2026-01-22T17:24:06.452Z</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>NDgyNDM2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>MTU0OGJhYjItYzE4NS00NGNmLThhOGItYzA1MzhmNTNjODJlOjU3MDE2</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3574,57 +3610,58 @@
           <t>350</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>2026-01-29T12:16:04.953Z</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>2026-01-22T13:01:41.368Z</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>YmEwMmQ1NzItYmIwMi00NTAxLWI4NWYtYmZiODY3NjIwZmRhOjU3MDE2</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3665,61 +3702,62 @@
           <t>478</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>2025-11-03T19:49:41.839Z</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>MmJlOTE4ZTYtMjdkMy00NThjLWE0ODUtYjczNjgwYjM3NWJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3760,65 +3798,66 @@
           <t>9000</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>jose da silva</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>HENRIQUE</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>YmViOGRmMjAtM2EwYy00NTFkLTkwNzctODkwYmM4MzA5NGQ0OjU3MDE2</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3859,61 +3898,62 @@
           <t>1298.9</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>2025-11-06T15:28:06.348Z</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3954,65 +3994,66 @@
           <t>1535</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>rffccfc</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4049,57 +4090,58 @@
           <t>40.894999999999996</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>2025-10-20T12:54:09.917Z</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>YTg2MWYxNTktMTEyNi00YWYxLWI4MmMtNzBlODk1NDQwMjE3OjU3MDE2</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4140,61 +4182,62 @@
           <t>47370</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Recusada</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>2025-08-15T18:20:20.020Z</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>2025-08-08T18:24:47.000Z</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>RAFAEL BARBOZA</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>2025-08-08T18:23:10.037Z</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>NzE0ZTQzMTctOWNiOC00OTI2LTgyOTItOWY5NzYxZDE3OGQxOjU3MDE2</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>refused</t>
         </is>
@@ -4235,61 +4278,62 @@
           <t>451.5</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>2025-12-19T16:01:13.514Z</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>2025-12-12T16:02:27.309Z</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>MzMxMDI2Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>ZWFiZTI5NDgtMzY0Ny00ODVkLThmNjEtODhjMGI2N2Q4Nzk2OjU3MDE2</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4326,61 +4370,62 @@
           <t>0.01</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>2024-09-12T20:48:10.536Z</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>2024-09-05T20:49:15.417Z</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>NDIxMTExMTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>ZmU4N2U3MGQtMzJiMi00MDhlLTljNzktZTRmN2M1ZDcyNzUwOjU3MDE2</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4421,57 +4466,58 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>2026-01-23T17:25:57.681Z</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>2026-01-16T17:30:58.730Z</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>NDgyNTk1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>MzMzMDQ3ZTYtMzU1OC00MTZjLWExZGYtNWU4MTg4ZmY2YzdhOjU3MDE2</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4522,61 +4568,62 @@
           <t>1700</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>2025-09-02T14:01:32.021Z</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>NTU4NTRiMjItMTA0Yi00ZDEzLThiMDktNzdjYzcxMTFmNzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4617,57 +4664,58 @@
           <t>5996.77</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>OTNhMDBkOGItMzEyYy00MzVkLTlmYzItY2I4NWU2ZTQ5MzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4708,61 +4756,62 @@
           <t>490.38</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>2025-11-13T15:27:36.746Z</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>2025-11-06T15:27:46.917Z</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4803,57 +4852,58 @@
           <t>428</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>2026-02-02T19:59:46.198Z</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>2026-01-26T20:04:54.521Z</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>MzQwMzM1ODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>ZjUzOGNhMTktYmI4Yi00MmUwLTk4ZDYtYzQyNzk3M2U2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4894,57 +4944,58 @@
           <t>2123.15</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>2025-11-04T13:33:37.491Z</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>2025-10-28T14:06:21.222Z</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>MjIwOTU3OGEtZGZlNi00Njk1LThhZWQtNjM5YzVjZjJmZTg5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4985,65 +5036,66 @@
           <t>511.65999999999997</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>2025-11-10T14:43:09.194Z</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>Viktor Chagas</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>2025-11-03T15:08:36.141Z</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>ZmU3NjFlZTktOWMxMy00OWM5LTlkZWItZjU0NGMzZjM3YTBkOjU3MDE2</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5084,65 +5136,66 @@
           <t>552</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Cancelada</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>2026-02-02T19:52:49.086Z</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>2026-01-27T12:28:33.000Z</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>2026-01-27T12:28:33.000Z</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>2026-01-26T19:59:17.023Z</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>MzM3ODQxNDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>MTZkNGJlZmQtNjNlNC00MWQ1LWEzNTEtODYxOWM3N2JmMzQ3OjU3MDE2</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -5185,61 +5238,62 @@
           <t>350</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>2025-12-09T18:46:05.954Z</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>2025-12-02T18:53:10.136Z</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5280,61 +5334,62 @@
           <t>979.73</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>2025-11-13T15:27:16.361Z</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>2025-11-06T15:27:31.134Z</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5375,61 +5430,62 @@
           <t>1224.475</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>2026-01-02T18:34:01.969Z</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>2025-12-26T18:48:40.881Z</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5466,61 +5522,62 @@
           <t>1172.55</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>2025-10-20T12:26:24.223Z</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>ZjQzMjRhOTEtZWM2NC00ZWUzLWFmNWItODM5NDliOWM2MjkzOjU3MDE2</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5561,65 +5618,66 @@
           <t>850.76</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
         <is>
           <t>Cancelada</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>2026-01-27T19:00:18.732Z</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>2026-01-20T19:19:25.000Z</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>2026-01-20T19:19:25.000Z</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>2026-01-20T19:17:25.784Z</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -5660,61 +5718,62 @@
           <t>683</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>2026-01-21T15:16:56.016Z</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>2026-01-14T15:28:26.334Z</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>NmQyZWFkMDctOWI5NC00YjQxLTgyZjYtN2VjYTAyYzM5ZTFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>NDgzNTU3MTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Zjk2NjZmMDUtZjI0Ny00MTQxLWJmMmItMzZhOWRkNzNlYzgwOjU3MDE2</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5759,61 +5818,62 @@
           <t>1047.65</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>2025-10-07T18:22:28.553Z</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5850,65 +5910,66 @@
           <t>40.894999999999996</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>2025-11-11T15:57:22.457Z</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
         <is>
           <t>Marcos</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/e9de7ba0-386a-464d-8581-a8798001ad78/signatures/a05c1641-9b6c-465a-90ae-a4510b4e3986.png</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>2025-11-04T15:57:50.841Z</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>YTg2MWYxNTktMTEyNi00YWYxLWI4MmMtNzBlODk1NDQwMjE3OjU3MDE2</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5950,61 +6011,62 @@
           <t>549.22</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>2025-10-06T19:05:55.326Z</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>MTcwZjFjYjQtMmE0OC00ZTYyLTg4ODAtZjBlOGU3M2I1MmExOjU3MDE2</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -6045,61 +6107,62 @@
           <t>7000</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>2026-02-06T18:27:35.984Z</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>2026-01-30T18:40:19.770Z</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>MDU1N2Q3Y2ItZmMxYi00OGVhLThkNDUtNzE5OGI0YjUwMWJkOjU3MDE2</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>NDM1ODE5OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>NzYwMWZlNDAtMzg2Mi00YjcyLTgwYWEtYzdkNWM1YmZiYmZjOjU3MDE2</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -6140,57 +6203,58 @@
           <t>2123.15</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>2025-11-18T12:23:08.942Z</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>2025-11-11T12:25:14.798Z</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>MjIwOTU3OGEtZGZlNi00Njk1LThhZWQtNjM5YzVjZjJmZTg5OjU3MDE2</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -6227,69 +6291,70 @@
           <t>956.025</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>2025-11-21T18:23:47.104Z</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
         <is>
           <t>Débora Mendes Mangaba</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/fbbec352-79e6-41e3-9553-a70ca4dd9b61/signatures/e629a18e-6cbe-4b79-8890-7071450b92a9.png</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>2025-11-14T18:28:52.343Z</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>ZWI1NTJkMzAtNjEwMS00NjM1LWE5MzYtOWE2ZTAwYjY2ZjgyOjU3MDE2</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>MzQwMzM1ODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>ZjUzOGNhMTktYmI4Yi00MmUwLTk4ZDYtYzQyNzk3M2U2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6330,61 +6395,62 @@
           <t>1197.8</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>2026-01-02T18:19:58.819Z</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>2025-12-26T18:30:18.349Z</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>NDU4ZDY0OTgtYjQwNy00MTdhLWE5YjYtNTg5ZDcyNGExMTQ1OjU3MDE2</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>NTE2MTc5NTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>ZTRkNTk4YzgtZTAxMi00ZWVkLWJkZTgtYTBkMjEzYmNkZjFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>expired</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:Z62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,60 +492,70 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>approvedAt</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>canceledAt</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>approvedBy</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>createdBy</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>approvedSignature</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>labels</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>order.id</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>discount.type</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>discount.value</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>discount.total</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>customer.id</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>location.id</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>status_original</t>
         </is>
@@ -631,48 +641,54 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>2025-11-11T16:06:07.949Z</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>NTYyNjA5ODctODA0MS00ODJlLWE1MTQtOTY0ZTQyZWRjOTYwOjU3MDE2</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>NDgyMzQxODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>NmFiMDUyZTMtMmRkMi00NWYwLWI1YzAtNzI5N2NmMGJiMzZhOjU3MDE2</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -721,58 +737,68 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-14T16:07:30.000Z</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Edina K O Mishima</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/1774f003-3175-4be8-801c-c7e958af19a8/signatures/650d7c22-e91c-4757-9ac9-9ad5beab0def.png</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2025-11-11T15:48:38.327Z</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>OTRkZmU3YjYtNDc4OC00OWJlLTk2OWMtYmQ5Y2Q4ZWRiMTY3OjU3MDE2</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>NDgzNDgwNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>NGNlYTU1YmYtMjg4My00OWI2LWE5YjEtNGEzNTNmZWU3MzZhOjU3MDE2</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -827,48 +853,54 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>2025-11-05T13:06:35.085Z</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>ZWMwNWE3NTgtODkyOC00ZjE5LWI0YTgtYjY0NmYwMDY2OGIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>NDE2MTc1Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>ZDg5NzUyMzktNDc5NS00NDU2LTg0MmItMjZhZjE2MWI3MWUzOjU3MDE2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -919,48 +951,54 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>2025-12-11T21:29:54.203Z</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>ZjZiNTJjY2UtNDFhMS00NjllLTkyNDEtMjIzYmY5ODE2NmJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1015,44 +1053,50 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>2026-01-30T18:45:35.907Z</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1109,50 +1153,56 @@
           <t>2026-01-22T14:57:37.000Z</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>2026-01-22T14:57:37.000Z</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>2026-01-22T14:40:07.831Z</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>YmEwMmQ1NzItYmIwMi00NTAxLWI4NWYtYmZiODY3NjIwZmRhOjU3MDE2</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -1203,48 +1253,54 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>IRACILDA LOPES</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>2024-08-07T17:45:02.123Z</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>MDIzNDM2N2QtZGJmOS00YjhlLTk2ZjUtZWE2N2NlMGVhYjljOjU3MDE2</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1297,54 +1353,64 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-08-28T15:42:36.000Z</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Rafael Machado Barboza</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>2025-08-28T15:35:41.479Z</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1403,48 +1469,54 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>2025-12-02T21:20:54.686Z</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1495,48 +1567,54 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>2025-10-02T21:19:25.794Z</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>MzQwNDRlN2UtMzgxYi00Nzc5LTk1MGItYTY3ODczZDg4NWM0OjU3MDE2</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1591,44 +1669,50 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>2026-01-20T19:19:08.741Z</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1685,58 +1769,68 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-10-03T17:36:05.000Z</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Joana D’Arc Oliveira </t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>MjU3OWZlNzYtYWVlNC00ODU0LWEyYTUtNDdkMWI2ZGY5ZDlmOjU3MDE2</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -1787,48 +1881,54 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1879,48 +1979,54 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>2025-09-29T18:38:37.635Z</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1971,48 +2077,54 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>2025-10-08T21:12:33.362Z</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>NDgzNDc2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>ZThkYWNiNmItMDliOS00Y2Y0LTgyNjgtOGU5OTk4NzQ3MmNkOjU3MDE2</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2068,48 +2180,54 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>2025-12-12T16:00:42.963Z</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>MzMxMDI2Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>ZWFiZTI5NDgtMzY0Ny00ODVkLThmNjEtODhjMGI2N2Q4Nzk2OjU3MDE2</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2166,48 +2284,54 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>2025-12-17T21:33:20.182Z</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2258,48 +2382,54 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>2025-11-07T16:26:09.914Z</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>ZjZiNTJjY2UtNDFhMS00NjllLTkyNDEtMjIzYmY5ODE2NmJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2354,48 +2484,54 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>2025-12-08T20:11:36.676Z</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>M2EzOTI5YTItODc3Zi00NTJlLTk1NDktMmU5YWRiMWMwZmQ1OjU3MDE2</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>NDgzNTU4Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>NTk1Y2ZkMTYtMTk4YS00OTE4LWI5YzMtZjcwMTliOTdlNDVjOjU3MDE2</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2454,48 +2590,54 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>2025-10-10T13:07:18.487Z</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>NDgyMzMyODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>NTg2M2M0ZTEtMThhNC00Y2YyLWFhNDktYTViMTdhYzE0MmZmOjU3MDE2</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2558,48 +2700,54 @@
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>2025-11-17T15:14:20.735Z</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>refused</t>
         </is>
@@ -2655,48 +2803,54 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>2025-11-18T21:53:35.934Z</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>NjYwZjY1NTAtNjFmZS00N2NmLTlmZTktMzY2ZWVjNmViZGJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>NTgwMDkyOTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>YTg3MTBjZDAtMzUwOC00OWNmLWIwMTAtMzMwNGVkOTA5ZWI0OjU3MDE2</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2763,44 +2917,50 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>NTU4NTRiMjItMTA0Yi00ZDEzLThiMDktNzdjYzcxMTFmNzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2859,44 +3019,50 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>RAFAEL BARBOZA</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>2025-08-08T18:27:17.728Z</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>NzE0ZTQzMTctOWNiOC00OTI2LTgyOTItOWY5NzYxZDE3OGQxOjU3MDE2</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2956,48 +3122,54 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>2025-12-09T20:21:45.714Z</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>MzIyOGRmMDAtMThlNi00NTc3LTk2MzctYmVjM2QxYmZlOWYwOjU3MDE2</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>NTg1NDM3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>M2NhMmM5M2MtNWIwNi00OWQwLWFmODgtYTQzNmJiOTUyM2EzOjU3MDE2</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3050,54 +3222,64 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-12-01T12:33:02.000Z</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>douglas simao</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>2025-12-01T12:28:02.404Z</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>NDUwNzM2Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>ZjBjMzdjOTgtNWY3Yi00ZGQ5LTgwNTktMDZkMjI4YTAzYTAwOjU3MDE2</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3152,48 +3334,54 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>OTNhMDBkOGItMzEyYy00MzVkLTlmYzItY2I4NWU2ZTQ5MzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3248,48 +3436,54 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>2025-12-04T15:21:12.082Z</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>Y2NjZDRjMTgtOWYwOC00YjUwLWFiNzktOGU0NGNhZTQzMTg3OjU3MDE2</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>MzUzMTEwNTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>NTM2Nzc5ZjUtZjA3MS00NzY0LTkyNmMtNzQwNmNlZDgzZjEwOjU3MDE2</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3340,48 +3534,54 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>2025-09-29T18:44:47.397Z</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3440,44 +3640,50 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3532,44 +3738,50 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>2026-01-22T17:24:06.452Z</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>NDgyNDM2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>MTU0OGJhYjItYzE4NS00NGNmLThhOGItYzA1MzhmNTNjODJlOjU3MDE2</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3624,44 +3836,50 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>2026-01-22T13:01:41.368Z</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>YmEwMmQ1NzItYmIwMi00NTAxLWI4NWYtYmZiODY3NjIwZmRhOjU3MDE2</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3716,48 +3934,54 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>2025-11-03T19:49:41.839Z</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>MmJlOTE4ZTYtMjdkMy00NThjLWE0ODUtYjczNjgwYjM3NWJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -3810,54 +4034,64 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2023-05-31T21:58:11.000Z</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>jose da silva</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>HENRIQUE</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>YmViOGRmMjAtM2EwYy00NTFkLTkwNzctODkwYmM4MzA5NGQ0OjU3MDE2</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3912,48 +4146,54 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>2025-11-06T15:28:06.348Z</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4006,54 +4246,64 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2025-08-28T16:13:23.000Z</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>rffccfc</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>NWY5N2U0ZjYtNjA5Zi00YTkzLWE2ZmQtNjI2YmFhOTU1Y2UzOjU3MDE2</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4104,44 +4354,50 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>YTg2MWYxNTktMTEyNi00YWYxLWI4MmMtNzBlODk1NDQwMjE3OjU3MDE2</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4200,44 +4456,50 @@
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>RAFAEL BARBOZA</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>2025-08-08T18:23:10.037Z</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>NzE0ZTQzMTctOWNiOC00OTI2LTgyOTItOWY5NzYxZDE3OGQxOjU3MDE2</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>refused</t>
         </is>
@@ -4292,48 +4554,54 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>2025-12-12T16:02:27.309Z</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
         <is>
           <t>OTYwNmY5MTktMmQxYi00NzI2LTg3MTYtZTJmMGE1MjE2NjFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>MzMxMDI2Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>ZWFiZTI5NDgtMzY0Ny00ODVkLThmNjEtODhjMGI2N2Q4Nzk2OjU3MDE2</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4384,48 +4652,54 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>2024-09-05T20:49:15.417Z</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
         <is>
           <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>NDIxMTExMTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>ZmU4N2U3MGQtMzJiMi00MDhlLTljNzktZTRmN2M1ZDcyNzUwOjU3MDE2</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4480,44 +4754,50 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>2026-01-16T17:30:58.730Z</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>NDgyNTk1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>MzMzMDQ3ZTYtMzU1OC00MTZjLWExZGYtNWU4MTg4ZmY2YzdhOjU3MDE2</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4582,48 +4862,54 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>2025-09-02T14:01:32.021Z</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
         <is>
           <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>NTU4NTRiMjItMTA0Yi00ZDEzLThiMDktNzdjYzcxMTFmNzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4678,44 +4964,50 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>OTNhMDBkOGItMzEyYy00MzVkLTlmYzItY2I4NWU2ZTQ5MzU5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4770,48 +5062,54 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>2025-11-06T15:27:46.917Z</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4866,44 +5164,50 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>2026-01-26T20:04:54.521Z</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>MzQwMzM1ODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>ZjUzOGNhMTktYmI4Yi00MmUwLTk4ZDYtYzQyNzk3M2U2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4958,44 +5262,50 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>2025-10-28T14:06:21.222Z</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>MjIwOTU3OGEtZGZlNi00Njk1LThhZWQtNjM5YzVjZjJmZTg5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5048,54 +5358,64 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2025-11-03T15:12:31.000Z</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
         <is>
           <t>Viktor Chagas</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>2025-11-03T15:08:36.141Z</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>ZmU3NjFlZTktOWMxMy00OWM5LTlkZWItZjU0NGMzZjM3YTBkOjU3MDE2</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -5152,50 +5472,56 @@
           <t>2026-01-27T12:28:33.000Z</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>2026-01-27T12:28:33.000Z</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>2026-01-26T19:59:17.023Z</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>MzM3ODQxNDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>MTZkNGJlZmQtNjNlNC00MWQ1LWEzNTEtODYxOWM3N2JmMzQ3OjU3MDE2</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -5252,48 +5578,54 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>2025-12-02T18:53:10.136Z</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
         <is>
           <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5348,48 +5680,54 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>2025-11-06T15:27:31.134Z</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>MzNhMjk0ZTUtMzI4MS00YTMwLTg2Y2QtYzM3YTQ0OTAyNzI5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5444,48 +5782,54 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>2025-12-26T18:48:40.881Z</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
         <is>
           <t>ODAxNDQ5MTMtNDYwMi00MjhmLWE1MWUtMWY1Y2I5NGIxY2Y1OjU3MDE2</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>MzMzMDQ1Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>ZTU1NzI4MzEtZTkzNS00ZWIzLTk4MTktMGE3MTZhOTE1NDZlOjU3MDE2</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5536,48 +5880,54 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
         <is>
           <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>ZjQzMjRhOTEtZWM2NC00ZWUzLWFmNWItODM5NDliOWM2MjkzOjU3MDE2</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5634,50 +5984,56 @@
           <t>2026-01-20T19:19:25.000Z</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>2026-01-20T19:19:25.000Z</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
         <is>
           <t>Lucas Uenishi Tada</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>2026-01-20T19:17:25.784Z</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>NDM1ODE3Nzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>ZDBlYTE4ZjgtNTRlNS00YjQ2LWIwZDEtZmM2MDc4ZTFhYjY1OjU3MDE2</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>canceled</t>
         </is>
@@ -5732,48 +6088,54 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>2026-01-14T15:28:26.334Z</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
         <is>
           <t>NmQyZWFkMDctOWI5NC00YjQxLTgyZjYtN2VjYTAyYzM5ZTFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>NDgzNTU3MTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Zjk2NjZmMDUtZjI0Ny00MTQxLWJmMmItMzZhOWRkNzNlYzgwOjU3MDE2</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5832,48 +6194,54 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>2025-10-07T18:22:28.553Z</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
         <is>
           <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>MWUzYmI1OWItNmZiNC00ODg1LTg0ODktOTlmY2IyZWYxNWIxOjU3MDE2</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5922,54 +6290,64 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2025-11-04T16:26:35.000Z</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
         <is>
           <t>Marcos</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/e9de7ba0-386a-464d-8581-a8798001ad78/signatures/a05c1641-9b6c-465a-90ae-a4510b4e3986.png</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>2025-11-04T15:57:50.841Z</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>YTg2MWYxNTktMTEyNi00YWYxLWI4MmMtNzBlODk1NDQwMjE3OjU3MDE2</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6025,48 +6403,54 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>MTcwZjFjYjQtMmE0OC00ZTYyLTg4ODAtZjBlOGU3M2I1MmExOjU3MDE2</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -6121,48 +6505,54 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>2026-01-30T18:40:19.770Z</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
         <is>
           <t>MDU1N2Q3Y2ItZmMxYi00OGVhLThkNDUtNzE5OGI0YjUwMWJkOjU3MDE2</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>NDM1ODE5OTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>NzYwMWZlNDAtMzg2Mi00YjcyLTgwYWEtYzdkNWM1YmZiYmZjOjU3MDE2</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -6217,44 +6607,50 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>2025-11-11T12:25:14.798Z</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>MjIwOTU3OGEtZGZlNi00Njk1LThhZWQtNjM5YzVjZjJmZTg5OjU3MDE2</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -6303,58 +6699,68 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2025-11-19T11:42:17.000Z</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
         <is>
           <t>Débora Mendes Mangaba</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/fbbec352-79e6-41e3-9553-a70ca4dd9b61/signatures/e629a18e-6cbe-4b79-8890-7071450b92a9.png</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>2025-11-14T18:28:52.343Z</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
         <is>
           <t>ZWI1NTJkMzAtNjEwMS00NjM1LWE5MzYtOWE2ZTAwYjY2ZjgyOjU3MDE2</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>MzQwMzM1ODo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>ZjUzOGNhMTktYmI4Yi00MmUwLTk4ZDYtYzQyNzk3M2U2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -6409,48 +6815,54 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>2025-12-26T18:30:18.349Z</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
         <is>
           <t>NDU4ZDY0OTgtYjQwNy00MTdhLWE5YjYtNTg5ZDcyNGExMTQ1OjU3MDE2</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>NTE2MTc5NTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>ZTRkNTk4YzgtZTAxMi00ZWVkLWJkZTgtYTBkMjEzYmNkZjFiOjU3MDE2</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
